--- a/data/season_2025/next_games/next_games.xlsx
+++ b/data/season_2025/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,44 +459,44 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Bet365_Match_Odds_Tie</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Pinnacle_Match_Odds_Away</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Pinnacle_Match_Odds_Draw</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Pinnacle_Match_Odds_Home</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Bet365_Btts_No</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Bet365_Btts_Yes</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Pinnacle_Btts_No</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Pinnacle_Btts_Yes</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Bet365_Lines_Goals_Over_1.5</t>
-        </is>
-      </c>
       <c r="O1" t="inlineStr">
         <is>
           <t>Bet365_Lines_Goals_Over_2.5</t>
@@ -504,35 +504,20 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Under_1.5</t>
+          <t>Bet365_Lines_Goals_Under_2.5</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Under_2.5</t>
+          <t>Pinnacle_Lines_Goals_Over_2.5</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_1.5</t>
+          <t>Pinnacle_Lines_Goals_Under_2.5</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Over_2.5</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_1.5</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_2.5</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
         <is>
           <t>Para mais mercados visite o site</t>
         </is>
@@ -541,78 +526,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Boyacá Chicó vs Deportes Tolima</t>
+          <t>Argentinos Juniors vs Lanús</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-23 19:00:00</t>
+          <t>2026-03-27 00:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
         </is>
@@ -621,230 +603,201 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>J1 100 Year Vision League - J1-100</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Castellón vs Cultural Leonesa</t>
+          <t>Vissel Kobe vs Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-23 19:30:00</t>
+          <t>2026-03-27 10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7.69</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Santa Fe vs Independiente Medellín</t>
+          <t>Córdoba vs Mirandés</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-23 21:10:00</t>
+          <t>2026-03-27 18:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Estudiantes vs Central Cordoba SdE</t>
+          <t>Rionegro Águilas vs Alianza Petrolera</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-23 22:00:00</t>
+          <t>2026-03-27 21:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -854,594 +807,313 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba vs Rionegro Águilas</t>
+          <t>Atlético Bucaramanga vs Santa Fe</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-23 23:20:00</t>
+          <t>2026-03-28 01:10:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>J1 100 Year Vision League - J1-100</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Huracán vs Barracas Central</t>
+          <t>Machida Zelvia vs Kawasaki Frontale</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-24 00:15:00</t>
+          <t>2026-03-28 05:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>J2/J3 100 Year Vision League - None</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado vs Montevideo City Torque</t>
+          <t>Nara Club vs Zweigen Kanazawa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-24 17:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
+          <t>2026-03-28 05:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>J2/J3 100 Year Vision League - None</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liverpool vs Central Español</t>
+          <t>Gifu vs Parceiro Nagano</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-24 20:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3.63</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
+          <t>2026-03-28 05:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J2/J3 100 Year Vision League - None</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deportivo Pereira vs Cúcuta Deportivo</t>
+          <t>Fujieda MYFC vs Consadole Sapporo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03-24 20:30:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2.43</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
+          <t>2026-03-28 05:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J2/J3 100 Year Vision League - None</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Junior FC vs Atlético Bucaramanga</t>
+          <t>Ventforet Kofu vs Omiya Ardija</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-24 23:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
+          <t>2026-03-28 05:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>J2/J3 100 Year Vision League - None</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nacional vs Cerro Largo</t>
+          <t>Yokohama vs Shonan Bellmare</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-24 23:30:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6.76</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+          <t>2026-03-28 05:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J2/J3 100 Year Vision League - None</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fortaleza CEIF vs Deportivo Pasto</t>
+          <t>ThespaKusatsu Gunma vs Tochigi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-03-25 01:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3.67</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+          <t>2026-03-28 05:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1450,389 +1122,371 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>K League 1 - KOR KL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Albion vs Wanderers</t>
+          <t>Pohang Steelers vs Gangwon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-03-25 17:00:00</t>
+          <t>2026-03-28 06:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cerro vs Juventud</t>
+          <t>Ceuta vs Cádiz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-03-25 20:00:00</t>
+          <t>2026-03-28 13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deportivo Riestra vs San Lorenzo</t>
+          <t>Granada vs Huesca</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-03-25 22:00:00</t>
+          <t>2026-03-28 15:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Boston River vs Peñarol</t>
+          <t>Real Valladolid vs Burgos</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-03-25 23:30:00</t>
+          <t>2026-03-28 15:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>6.06</t>
-        </is>
-      </c>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>América de Cali vs Llaneros</t>
+          <t>Málaga vs Leganés</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-03-26 01:00:00</t>
+          <t>2026-03-28 17:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1842,55 +1496,55 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Racing vs Atlético Progreso</t>
+          <t>Wanderers vs Cerro</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-03-26 16:00:00</t>
+          <t>2026-03-28 19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -1898,199 +1552,210 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Danubio vs Defensor Sporting</t>
+          <t>Albacete vs Castellón</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-03-26 19:00:00</t>
+          <t>2026-03-28 20:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Argentinos Juniors vs Lanús</t>
+          <t>Sporting Gijón vs Deportivo La Coruña</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-03-27 00:00:00</t>
+          <t>2026-03-28 20:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J1 100 Year Vision League - J1-100</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vissel Kobe vs Sanfrecce Hiroshima</t>
+          <t>Cúcuta Deportivo vs Boyacá Chicó</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-03-27 10:00:00</t>
+          <t>2026-03-28 21:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -2098,45 +1763,42 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Córdoba vs Mirandés</t>
+          <t>Montevideo City Torque vs Nacional</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-03-27 18:00:00</t>
+          <t>2026-03-28 22:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5.06</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -2146,9 +1808,6 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2158,23 +1817,55 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rionegro Águilas vs Alianza Petrolera</t>
+          <t>Deportes Tolima vs Jaguares de Córdoba</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-03-27 21:00:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+          <t>2026-03-28 23:10:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2182,13 +1873,1628 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deportivo Cali vs Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-03-29 01:20:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>9.54</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Roasso Kumamoto vs Kagoshima United</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-03-29 04:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Vanraure Hachinohe vs Sagamihara</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-03-29 04:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Giravanz Kitakyushu vs Ryūkyū</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Renofa Yamaguchi vs Oita Trinita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gainare Tottori vs Sagan Tosu</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rayluck Shiga vs Tegevajaro Miyazaki</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tokushima Vortis vs Kochi United</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Kamatamare Sanuki vs Ehime</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Osaka vs Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kataller Toyama vs Imabari</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Iwaki vs Júbilo Iwata</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Fukushima United vs Matsumoto Yamaga</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Montedio Yamagata vs Tochigi City</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>J2/J3 100 Year Vision League - None</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Blaublitz Akita vs Vegalta Sendai</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-03-29 05:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SD Eibar vs Las Palmas</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-03-29 12:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Atlético Progreso vs Liverpool</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-03-29 13:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cultural Leonesa vs FC Andorra</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-03-29 14:15:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Liga Portugal 2 - PRT SL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>União de Leiria vs Paços de Ferreira</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-03-29 14:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Juventud vs Boston River</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-03-29 16:00:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Real Zaragoza vs Racing Santander</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-03-29 16:30:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>La Liga 2 - ESP S</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Almería vs Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-03-29 19:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4.16</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Defensor Sporting vs Albion</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-03-29 19:00:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá vs Junior FC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-03-29 21:10:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Serie A - BRA CB</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Athletico PR vs Botafogo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:30:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Peñarol vs Racing</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:30:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>6.28</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto vs Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-03-29 23:20:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Llaneros vs Once Caldas</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-03-30 01:30:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cerro Largo vs Danubio</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-03-30 21:00:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Independiente Medellín vs América de Cali</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-03-30 23:10:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/season_2025/next_games/next_games.xlsx
+++ b/data/season_2025/next_games/next_games.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S51"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,65 +459,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Bet365_Match_Odds_Tie</t>
+          <t>Pinnacle_Match_Odds_Away</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Pinnacle_Match_Odds_Away</t>
+          <t>Pinnacle_Match_Odds_Draw</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Pinnacle_Match_Odds_Draw</t>
+          <t>Pinnacle_Match_Odds_Home</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Pinnacle_Match_Odds_Home</t>
+          <t>Bet365_Btts_No</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Bet365_Btts_No</t>
+          <t>Bet365_Btts_Yes</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Bet365_Btts_Yes</t>
+          <t>Pinnacle_Btts_No</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Pinnacle_Btts_No</t>
+          <t>Pinnacle_Btts_Yes</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Pinnacle_Btts_Yes</t>
+          <t>Bet365_Lines_Goals_Over_2.5</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Over_2.5</t>
+          <t>Bet365_Lines_Goals_Under_2.5</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Bet365_Lines_Goals_Under_2.5</t>
+          <t>Pinnacle_Lines_Goals_Over_2.5</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Pinnacle_Lines_Goals_Over_2.5</t>
+          <t>Pinnacle_Lines_Goals_Under_2.5</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
-        <is>
-          <t>Pinnacle_Lines_Goals_Under_2.5</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>Para mais mercados visite o site</t>
         </is>
@@ -526,75 +521,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SD Eibar vs Las Palmas</t>
+          <t>Independiente Medellín vs América de Cali</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-29 12:00:00</t>
+          <t>2026-03-30 23:10:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>https://www.quantumodds.xyz/</t>
         </is>
@@ -608,240 +594,205 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Atlético Progreso vs Liverpool</t>
+          <t>Cerro Largo vs Danubio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-29 13:00:00</t>
+          <t>2026-03-30 23:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cultural Leonesa vs FC Andorra</t>
+          <t>Central Español vs Deportivo Maldonado</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-29 14:15:00</t>
+          <t>2026-03-31 00:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Liga Portugal 2 - PRT SL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>União de Leiria vs Paços de Ferreira</t>
+          <t>Millonarios vs Fortaleza CEIF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-29 14:30:00</t>
+          <t>2026-03-31 01:20:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -851,17 +802,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Juventud vs Boston River</t>
+          <t>Atlético Progreso vs Liverpool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-29 16:00:00</t>
+          <t>2026-03-31 14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -871,50 +822,49 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -924,205 +874,199 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Real Zaragoza vs Racing Santander</t>
+          <t>Mirandés vs Albacete</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-29 16:30:00</t>
+          <t>2026-03-31 17:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Almería vs Real Sociedad II</t>
+          <t>Aldosivi vs Argentinos Juniors</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-29 19:00:00</t>
+          <t>2026-03-31 17:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4.54</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4.12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>6.14</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Defensor Sporting vs Albion</t>
+          <t>Deportivo La Coruña vs Córdoba</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-29 19:00:00</t>
+          <t>2026-03-31 18:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1130,457 +1074,407 @@
           <t>1.66</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá vs Junior FC</t>
+          <t>Real Valladolid vs Cádiz</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03-29 21:10:00</t>
+          <t>2026-03-31 19:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Primera Division - URY CL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Athletico PR vs Botafogo</t>
+          <t>Defensor Sporting vs Albion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-03-29 22:30:00</t>
+          <t>2026-03-31 22:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Peñarol vs Racing</t>
+          <t>Deportes Tolima vs Rionegro Águilas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-29 22:30:00</t>
+          <t>2026-04-01 01:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J1 100 Year Vision League - J1-100</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deportivo Pasto vs Atlético Nacional</t>
+          <t>Vissel Kobe vs Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-03-29 23:20:00</t>
+          <t>2026-04-01 10:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
           <t>1.80</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>J1 100 Year Vision League - J1-100</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Llaneros vs Once Caldas</t>
+          <t>Machida Zelvia vs FC Tokyo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-03-30 01:30:00</t>
+          <t>2026-04-01 10:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2.89</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cerro Largo vs Danubio</t>
+          <t>FC Andorra vs Málaga</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-03-30 21:00:00</t>
+          <t>2026-04-01 17:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1588,194 +1482,207 @@
           <t>1.72</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Independiente Medellín vs América de Cali</t>
+          <t>Burgos vs Ceuta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-03-30 23:10:00</t>
+          <t>2026-04-01 18:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Primera Division - URY CL</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Central Español vs Deportivo Maldonado</t>
+          <t>Huesca vs Cultural Leonesa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-03-31 00:00:00</t>
+          <t>2026-04-01 18:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Millonarios vs Fortaleza CEIF</t>
+          <t>Racing Santander vs Sporting Gijón</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-03-31 01:20:00</t>
+          <t>2026-04-01 19:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1783,59 +1690,54 @@
           <t>1.66</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mirandés vs Albacete</t>
+          <t>Alianza Petrolera vs Deportivo Pasto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:00</t>
+          <t>2026-04-01 21:10:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1843,295 +1745,295 @@
           <t>2.70</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aldosivi vs Argentinos Juniors</t>
+          <t>Internacional vs São Paulo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:00</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-04-01 22:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña vs Córdoba</t>
+          <t>Botafogo vs Mirassol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-03-31 18:00:00</t>
+          <t>2026-04-01 22:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>3.81</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Real Valladolid vs Cádiz</t>
+          <t>Bahia vs Athletico PR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-03-31 19:30:00</t>
+          <t>2026-04-01 23:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deportes Tolima vs Rionegro Águilas</t>
+          <t>Cruzeiro vs Vitória</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-01 01:00:00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>2026-04-01 23:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -2139,32 +2041,63 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J1 100 Year Vision League - J1-100</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vissel Kobe vs Shimizu S-Pulse</t>
+          <t>Lanús vs Platense</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-01 10:00:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>2026-04-01 23:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -2172,32 +2105,63 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J1 100 Year Vision League - J1-100</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Machida Zelvia vs FC Tokyo</t>
+          <t>Coritiba vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-01 10:00:00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>2026-04-01 23:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -2205,32 +2169,63 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FC Andorra vs Málaga</t>
+          <t>Santa Fe vs Llaneros</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-01 17:00:00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>2026-04-01 23:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6.13</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -2238,95 +2233,105 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Burgos vs Ceuta</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-01 18:00:00</t>
+          <t>2026-04-02 00:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Huesca vs Cultural Leonesa</t>
+          <t>Atlético Nacional vs Cúcuta Deportivo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-01 18:00:00</t>
+          <t>2026-04-02 01:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10.58</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2336,7 +2341,6 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2346,22 +2350,54 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Racing Santander vs Sporting Gijón</t>
+          <t>Las Palmas vs Granada</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-01 19:30:00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>2026-04-02 17:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -2369,32 +2405,63 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alianza Petrolera vs Deportivo Pasto</t>
+          <t>Castellón vs Almería</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-01 21:10:00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>2026-04-02 18:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -2402,243 +2469,262 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Internacional vs São Paulo</t>
+          <t>Real Sociedad II vs SD Eibar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-01 22:30:00</t>
+          <t>2026-04-02 18:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Botafogo vs Mirassol</t>
+          <t>Barracas Central vs Sarmiento</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-04-01 22:30:00</t>
+          <t>2026-04-02 18:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bahia vs Athletico PR</t>
+          <t>Boyacá Chicó vs Deportivo Pereira</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-04-01 23:00:00</t>
+          <t>2026-04-02 19:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>La Liga 2 - ESP S</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cruzeiro vs Vitória</t>
+          <t>Leganés vs Real Zaragoza</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-04-01 23:00:00</t>
+          <t>2026-04-02 19:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2648,33 +2734,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lanús vs Platense</t>
+          <t>Tigre vs Independiente Rivadavia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-01 23:00:00</t>
+          <t>2026-04-02 20:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>4.54</t>
-        </is>
-      </c>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2683,97 +2769,127 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coritiba vs Vasco da Gama</t>
+          <t>América de Cali vs Atlético Bucaramanga</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-01 23:30:00</t>
+          <t>2026-04-02 21:10:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Santa Fe vs Llaneros</t>
+          <t>Chapecoense vs Atlético Mineiro</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-01 23:30:00</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>2026-04-02 22:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -2781,7 +2897,6 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2791,62 +2906,49 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Santos vs Remo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-02 00:30:00</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>2026-04-02 22:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2856,22 +2958,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Atlético Nacional vs Cúcuta Deportivo</t>
+          <t>Jaguares de Córdoba vs Millonarios</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-02 01:30:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>2026-04-02 23:20:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -2879,30 +3001,41 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Las Palmas vs Granada</t>
+          <t>Talleres Córdoba vs Boca Juniors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-02 17:00:00</t>
+          <t>2026-04-02 23:30:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2912,22 +3045,21 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Super League - GRC SL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Castellón vs Almería</t>
+          <t>Panaitolikos vs Atromitos</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-02 18:00:00</t>
+          <t>2026-04-03 00:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2945,22 +3077,21 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Super League - GRC SL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Real Sociedad II vs SD Eibar</t>
+          <t>Kifisia vs Panserraikos</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-02 18:00:00</t>
+          <t>2026-04-03 00:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2978,371 +3109,543 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Super League - GRC SL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Barracas Central vs Sarmiento</t>
+          <t>Asteras Tripolis vs Larissa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-04-02 18:00:00</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>2026-04-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>3.58</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Boyacá Chicó vs Deportivo Pereira</t>
+          <t>Bragantino vs Flamengo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-02 19:00:00</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>2026-04-03 00:30:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>4.43</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3.68</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>La Liga 2 - ESP S</t>
+          <t>Serie A - BRA CB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Leganés vs Real Zaragoza</t>
+          <t>Palmeiras vs Grêmio</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-02 19:30:00</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>2026-04-03 00:30:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5.91</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga BetPlay - COL PA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tigre vs Independiente Rivadavia</t>
+          <t>Once Caldas vs Independiente Medellín</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-04-02 20:30:00</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+          <t>2026-04-03 01:30:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3.81</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Liga Portugal - PRT PL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>América de Cali vs Atlético Bucaramanga</t>
+          <t>Gil Vicente vs AVS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-04-02 21:10:00</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>2026-04-03 14:30:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8.76</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Liga Portugal 2 - PRT SL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chapecoense vs Atlético Mineiro</t>
+          <t>UD Oliveirense vs Portimonense SAD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-04-02 22:00:00</t>
+          <t>2026-04-03 14:30:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Serie A - BRA CB</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Santos vs Remo</t>
+          <t>Al Kholood vs Al Khaleej</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-04-02 22:00:00</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+          <t>2026-04-03 16:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6.47</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Liga BetPlay - COL PA</t>
+          <t>Pro League - SAU PL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba vs Millonarios</t>
+          <t>Al Ittihad vs Al Hazm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-04-02 23:20:00</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>2026-04-03 16:15:00</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5.84</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>8.08</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -3350,44 +3653,63 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Liga Profesional de Fútbol - ARG PD</t>
+          <t>Liga Portugal - PRT PL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Talleres Córdoba vs Boca Juniors</t>
+          <t>Vitória Guimarães vs Tondela</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-04-02 23:30:00</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+          <t>2026-04-03 17:00:00</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -3395,11 +3717,702 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pro League - SAU PL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Al Nassr vs Al Najma</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>18.74</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>22.29</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gimnasia y Esgrima Mendoza vs Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:00:00</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ligue 1 - FRA L1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Toulouse</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:45:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Pro League - BEL FDA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Antwerp vs Genk</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-04-03 18:45:00</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>La Liga - ESP PL</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano vs Elche</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-04-03 19:00:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Liga Portugal - PRT PL</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Sporting CP vs Santa Clara</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-04-03 19:30:00</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>5.68</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>12.83</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Boston River vs Wanderers</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-04-03 20:00:00</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unión Santa Fe vs Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-04-03 20:15:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4.92</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Liga Profesional de Fútbol - ARG PD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>San Lorenzo vs Estudiantes</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-04-03 22:30:00</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Liga BetPlay - COL PA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Fortaleza CEIF vs Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-04-03 23:20:00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Primera Division - URY CL</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Nacional vs Central Español</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-04-03 23:30:00</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
